--- a/data/trans_orig/P15B_tráfico-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15B_tráfico-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64524</t>
+          <t>63973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>35830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42881</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>59412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66103</t>
+          <t>64624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86533</t>
+          <t>85673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>75745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>72517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143456</t>
+          <t>141138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>169053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48610</t>
+          <t>48592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65209</t>
+          <t>65402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94285</t>
+          <t>93176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106788</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147717</t>
+          <t>147834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>168362</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60827</t>
+          <t>62227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60711</t>
+          <t>61695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91298</t>
+          <t>91979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122457</t>
+          <t>121057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146614</t>
+          <t>146093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75128</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94000</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205679</t>
+          <t>204998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236266</t>
+          <t>235282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87890</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100824</t>
+          <t>102105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140036</t>
+          <t>142249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198188</t>
+          <t>197796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228280</t>
+          <t>228397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401446</t>
+          <t>399233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>440658</t>
+          <t>439377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31421</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>41269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60747</t>
+          <t>61239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71891</t>
+          <t>72053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>96176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111788</t>
+          <t>110898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79874</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100441</t>
+          <t>99309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54276</t>
+          <t>54883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>71042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140501</t>
+          <t>140691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166320</t>
+          <t>165795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>30957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59832</t>
+          <t>60472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91877</t>
+          <t>91959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141207</t>
+          <t>140522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163989</t>
+          <t>164858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167875</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295391</t>
+          <t>295309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327436</t>
+          <t>326796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>22598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>76384</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67657</t>
+          <t>71635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>79773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>104726</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>96113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105134</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>44988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80610</t>
+          <t>82396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>105875</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>94604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107521</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>70805</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59572</t>
+          <t>66039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80943</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>168538</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>167738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182013</t>
+          <t>198939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>43012</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33432</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>59973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>75165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>50302</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>64897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>99563</t>
+          <t>109658</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>91039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121932</t>
+          <t>129652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144719</t>
+          <t>159260</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128769</t>
+          <t>143452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159102</t>
+          <t>174319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166040</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150816</t>
+          <t>165891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176123</t>
+          <t>193049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>310760</t>
+          <t>339747</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288391</t>
+          <t>319753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328260</t>
+          <t>358366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
